--- a/templates/fleet_cards_template.xlsx
+++ b/templates/fleet_cards_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7684DC07-54B2-4408-A867-7689F82EE7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E651AAA-FD01-4333-B1A4-D33D5D7CFB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9EC15B86-8430-4C82-96C7-45C8B0A5CDA7}"/>
   </bookViews>
@@ -519,10 +519,10 @@
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>426950</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>82850</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -552,7 +552,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="152400" y="101600"/>
-          <a:ext cx="3240000" cy="648000"/>
+          <a:ext cx="2800350" cy="692150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -564,14 +564,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>231775</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:colOff>225425</xdr:colOff>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>188595</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -601,7 +601,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="158750" y="9004300"/>
+          <a:off x="152400" y="8636000"/>
           <a:ext cx="3508375" cy="99695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -615,13 +615,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>188595</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -981,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BDDDB16-EB34-497B-8EB5-6244C2025B0F}">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.42578125" customWidth="1"/>
@@ -995,74 +995,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C9" s="1" t="s">
+    <row r="7" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="3:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="3:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="C12" s="2" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="3:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="3:14" ht="24" x14ac:dyDescent="0.25">
+      <c r="C10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="2" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="2" t="s">
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="2" t="s">
+      <c r="J10" s="3"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="4"/>
-    </row>
-    <row r="13" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="5"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="11"/>
-    </row>
-    <row r="14" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="3"/>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="11"/>
+    </row>
+    <row r="12" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="18"/>
+    </row>
+    <row r="13" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="18"/>
+    </row>
+    <row r="14" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="12"/>
       <c r="D14" s="13"/>
       <c r="E14" s="14"/>
@@ -1076,7 +1104,7 @@
       <c r="M14" s="17"/>
       <c r="N14" s="18"/>
     </row>
-    <row r="15" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="12"/>
       <c r="D15" s="13"/>
       <c r="E15" s="14"/>
@@ -1090,7 +1118,7 @@
       <c r="M15" s="17"/>
       <c r="N15" s="18"/>
     </row>
-    <row r="16" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="12"/>
       <c r="D16" s="13"/>
       <c r="E16" s="14"/>
@@ -1104,7 +1132,7 @@
       <c r="M16" s="17"/>
       <c r="N16" s="18"/>
     </row>
-    <row r="17" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="12"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
@@ -1118,7 +1146,7 @@
       <c r="M17" s="17"/>
       <c r="N17" s="18"/>
     </row>
-    <row r="18" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="12"/>
       <c r="D18" s="13"/>
       <c r="E18" s="14"/>
@@ -1132,7 +1160,7 @@
       <c r="M18" s="17"/>
       <c r="N18" s="18"/>
     </row>
-    <row r="19" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="12"/>
       <c r="D19" s="13"/>
       <c r="E19" s="14"/>
@@ -1146,7 +1174,7 @@
       <c r="M19" s="17"/>
       <c r="N19" s="18"/>
     </row>
-    <row r="20" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="12"/>
       <c r="D20" s="13"/>
       <c r="E20" s="14"/>
@@ -1160,7 +1188,7 @@
       <c r="M20" s="17"/>
       <c r="N20" s="18"/>
     </row>
-    <row r="21" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
@@ -1174,7 +1202,7 @@
       <c r="M21" s="17"/>
       <c r="N21" s="18"/>
     </row>
-    <row r="22" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="12"/>
       <c r="D22" s="13"/>
       <c r="E22" s="14"/>
@@ -1188,7 +1216,7 @@
       <c r="M22" s="17"/>
       <c r="N22" s="18"/>
     </row>
-    <row r="23" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="12"/>
       <c r="D23" s="13"/>
       <c r="E23" s="14"/>
@@ -1202,7 +1230,7 @@
       <c r="M23" s="17"/>
       <c r="N23" s="18"/>
     </row>
-    <row r="24" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="12"/>
       <c r="D24" s="13"/>
       <c r="E24" s="14"/>
@@ -1216,7 +1244,7 @@
       <c r="M24" s="17"/>
       <c r="N24" s="18"/>
     </row>
-    <row r="25" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="12"/>
       <c r="D25" s="13"/>
       <c r="E25" s="14"/>
@@ -1230,7 +1258,7 @@
       <c r="M25" s="17"/>
       <c r="N25" s="18"/>
     </row>
-    <row r="26" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="12"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
@@ -1244,7 +1272,7 @@
       <c r="M26" s="17"/>
       <c r="N26" s="18"/>
     </row>
-    <row r="27" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="12"/>
       <c r="D27" s="13"/>
       <c r="E27" s="14"/>
@@ -1258,7 +1286,7 @@
       <c r="M27" s="17"/>
       <c r="N27" s="18"/>
     </row>
-    <row r="28" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="12"/>
       <c r="D28" s="13"/>
       <c r="E28" s="14"/>
@@ -1272,7 +1300,7 @@
       <c r="M28" s="17"/>
       <c r="N28" s="18"/>
     </row>
-    <row r="29" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="12"/>
       <c r="D29" s="13"/>
       <c r="E29" s="14"/>
@@ -1286,7 +1314,7 @@
       <c r="M29" s="17"/>
       <c r="N29" s="18"/>
     </row>
-    <row r="30" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="12"/>
       <c r="D30" s="13"/>
       <c r="E30" s="14"/>
@@ -1300,7 +1328,7 @@
       <c r="M30" s="17"/>
       <c r="N30" s="18"/>
     </row>
-    <row r="31" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="12"/>
       <c r="D31" s="13"/>
       <c r="E31" s="14"/>
@@ -1314,7 +1342,7 @@
       <c r="M31" s="17"/>
       <c r="N31" s="18"/>
     </row>
-    <row r="32" spans="3:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="12"/>
       <c r="D32" s="13"/>
       <c r="E32" s="14"/>
@@ -1328,161 +1356,125 @@
       <c r="M32" s="17"/>
       <c r="N32" s="18"/>
     </row>
-    <row r="33" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="18"/>
-    </row>
-    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="12"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="18"/>
-    </row>
-    <row r="35" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="19"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="25"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+    <row r="33" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="25"/>
+    </row>
+    <row r="34" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+    </row>
+    <row r="36" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="P36" s="27"/>
+    </row>
+    <row r="37" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+    </row>
+    <row r="38" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="L33:N33"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
     <mergeCell ref="I29:K29"/>
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="L30:N30"/>
-    <mergeCell ref="J36:N36"/>
-    <mergeCell ref="A40:P40"/>
-    <mergeCell ref="A41:P41"/>
-    <mergeCell ref="A42:P42"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="F28:H28"/>
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="L28:N28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="J34:N34"/>
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A37:P37"/>
+    <mergeCell ref="A38:P38"/>
     <mergeCell ref="C26:E26"/>
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="L26:N26"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="L33:N33"/>
     <mergeCell ref="C24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="I24:K24"/>
@@ -1531,7 +1523,6 @@
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="L15:N15"/>
-    <mergeCell ref="C9:N10"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="I12:K12"/>
@@ -1540,6 +1531,15 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:K13"/>
     <mergeCell ref="L13:N13"/>
+    <mergeCell ref="C7:N8"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/fleet_cards_template.xlsx
+++ b/templates/fleet_cards_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E651AAA-FD01-4333-B1A4-D33D5D7CFB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1BB72D-2314-47B5-A378-501565D9D446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9EC15B86-8430-4C82-96C7-45C8B0A5CDA7}"/>
+    <workbookView xWindow="2115" yWindow="2115" windowWidth="21600" windowHeight="11385" xr2:uid="{9EC15B86-8430-4C82-96C7-45C8B0A5CDA7}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -144,15 +144,67 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -160,36 +212,88 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </top>
       <bottom style="thin">
         <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -197,10 +301,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -210,10 +314,10 @@
         <color theme="0" tint="-0.24994659260841701"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -223,265 +327,51 @@
       </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.24994659260841701"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -491,6 +381,80 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,13 +528,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:colOff>12700</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>225425</xdr:colOff>
+      <xdr:colOff>231775</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>188595</xdr:rowOff>
     </xdr:to>
@@ -601,7 +565,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="152400" y="8636000"/>
+          <a:off x="158750" y="8636000"/>
           <a:ext cx="3508375" cy="99695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -614,13 +578,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>196850</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>188595</xdr:rowOff>
     </xdr:to>
@@ -651,7 +615,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2216150" y="9004300"/>
+          <a:off x="2222500" y="8636000"/>
           <a:ext cx="3508375" cy="99695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -996,533 +960,456 @@
   <sheetData>
     <row r="1" spans="3:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
     </row>
     <row r="8" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
     </row>
     <row r="9" spans="3:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="3:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="2" t="s">
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="2" t="s">
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="2" t="s">
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="4"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
     </row>
     <row r="11" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="18"/>
     </row>
     <row r="12" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="20"/>
     </row>
     <row r="13" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="20"/>
     </row>
     <row r="14" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="20"/>
     </row>
     <row r="16" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="20"/>
     </row>
     <row r="17" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="20"/>
     </row>
     <row r="18" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="20"/>
     </row>
     <row r="19" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="20"/>
     </row>
     <row r="20" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="20"/>
     </row>
     <row r="21" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="20"/>
     </row>
     <row r="22" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="20"/>
     </row>
     <row r="23" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="20"/>
     </row>
     <row r="24" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="20"/>
     </row>
     <row r="25" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="20"/>
     </row>
     <row r="26" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="20"/>
     </row>
     <row r="27" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="20"/>
     </row>
     <row r="28" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="20"/>
     </row>
     <row r="29" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="20"/>
     </row>
     <row r="30" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="12"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="20"/>
     </row>
     <row r="31" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="12"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="18"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="20"/>
     </row>
     <row r="32" spans="3:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="20"/>
     </row>
     <row r="33" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="19"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="25"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
     </row>
     <row r="36" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
+      <c r="A36" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
     </row>
     <row r="37" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
     </row>
     <row r="38" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="101">
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="J34:N34"/>
-    <mergeCell ref="A36:P36"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="L15:N15"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="I12:K12"/>
@@ -1540,6 +1427,90 @@
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="L11:N11"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="J34:N34"/>
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A37:P37"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
